--- a/data/gravel not enough data/Lee Cougan Innova Supergravel 2025.xlsx
+++ b/data/gravel not enough data/Lee Cougan Innova Supergravel 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE28CCB-08D1-384A-AC23-40BE3EDBBC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291C55E8-5514-D344-AFFD-3E8F6724ECF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26820" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34180" yWindow="-23840" windowWidth="26820" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -70,12 +70,6 @@
     <t>L</t>
   </si>
   <si>
-    <t>...6</t>
-  </si>
-  <si>
-    <t>...7</t>
-  </si>
-  <si>
     <t>seat_tube_length</t>
   </si>
   <si>
@@ -226,9 +220,6 @@
     <t>fork_suspension</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>stem_suspension</t>
   </si>
   <si>
@@ -346,14 +337,32 @@
     <t>rider_max</t>
   </si>
   <si>
-    <t>a8:g33</t>
+    <t>a8:e33</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -364,6 +373,11 @@
       <color rgb="FF000000"/>
       <name val="Futura"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
     </font>
   </fonts>
   <fills count="2">
@@ -386,9 +400,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,13 +700,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -707,7 +722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -715,7 +730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -723,7 +738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -731,15 +746,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -755,19 +770,13 @@
       <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="G8" t="s">
+      <c r="B9" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
       </c>
       <c r="C9">
         <v>420</v>
@@ -779,12 +788,12 @@
         <v>515</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>590</v>
@@ -796,12 +805,12 @@
         <v>625</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -813,12 +822,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>428</v>
@@ -830,12 +839,12 @@
         <v>428</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>69</v>
@@ -847,12 +856,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <v>73</v>
@@ -864,12 +873,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>1107.5999999999999</v>
@@ -881,12 +890,12 @@
         <v>1143.7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>428.5</v>
@@ -900,10 +909,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C17">
         <v>581</v>
@@ -917,10 +926,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18">
         <v>616.1</v>
@@ -934,10 +943,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>310</v>
@@ -951,10 +960,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>80</v>
@@ -968,10 +977,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>710</v>
@@ -985,42 +994,60 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="C23">
+        <v>44</v>
+      </c>
+      <c r="D23">
+        <v>44</v>
+      </c>
+      <c r="E23">
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="C24">
+        <v>503.7</v>
+      </c>
+      <c r="D24">
+        <v>503.7</v>
+      </c>
+      <c r="E24">
+        <v>503.7</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <v>700</v>
@@ -1034,12 +1061,21 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="C30">
+        <v>50</v>
+      </c>
+      <c r="D30">
+        <v>50</v>
+      </c>
+      <c r="E30">
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C31">
         <v>55</v>
@@ -1053,12 +1089,12 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -1066,236 +1102,263 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" t="s">
-        <v>58</v>
+      <c r="A36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" t="s">
-        <v>60</v>
+      <c r="A37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>61</v>
+      <c r="A38" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>64</v>
+        <v>57</v>
+      </c>
+      <c r="B40" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>63</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45" t="s">
-        <v>72</v>
+        <v>65</v>
+      </c>
+      <c r="B45">
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>74</v>
-      </c>
-      <c r="B47" t="s">
-        <v>75</v>
+        <v>67</v>
+      </c>
+      <c r="B47">
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="B48" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>77</v>
-      </c>
-      <c r="B49" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>74</v>
+      </c>
+      <c r="B52" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="B53" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>84</v>
-      </c>
-      <c r="B54" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>87</v>
-      </c>
-      <c r="B56" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>81</v>
+      </c>
+      <c r="B57" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="B59" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>92</v>
-      </c>
-      <c r="B60" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>94</v>
-      </c>
-      <c r="B61" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>95</v>
-      </c>
-      <c r="B62" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>89</v>
+      </c>
+      <c r="B63" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>91</v>
+      </c>
+      <c r="B64" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="B65" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>100</v>
-      </c>
-      <c r="B67" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>102</v>
-      </c>
-      <c r="B68" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>99</v>
+      </c>
+      <c r="B71" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel not enough data/Lee Cougan Innova Supergravel 2025.xlsx
+++ b/data/gravel not enough data/Lee Cougan Innova Supergravel 2025.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel not enough data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291C55E8-5514-D344-AFFD-3E8F6724ECF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718073B9-568D-2D44-8252-D44842C1D815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34180" yWindow="-23840" windowWidth="26820" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8080" yWindow="3320" windowWidth="20720" windowHeight="14380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -46,9 +59,6 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://whytebikes.com/products/verro-gravel-adventure-bike?variant=55457665679733</t>
-  </si>
-  <si>
     <t>15-Jul-2025</t>
   </si>
   <si>
@@ -205,9 +215,6 @@
     <t>tire_width_max_700c</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
     <t>tire_width_max_650b</t>
   </si>
   <si>
@@ -316,24 +323,15 @@
     <t>frameset</t>
   </si>
   <si>
-    <t>3300</t>
-  </si>
-  <si>
     <t>base_build</t>
   </si>
   <si>
-    <t>5300</t>
-  </si>
-  <si>
     <t>custom_builds</t>
   </si>
   <si>
     <t>currency</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>rider_max</t>
   </si>
   <si>
@@ -356,6 +354,39 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>https://leecougan.com/en/bikes/gravel-bike/innova-supergravel</t>
+  </si>
+  <si>
+    <t>https://cdn.s2api.it/prod/2025/09/RISG_Mullet-GX_RK25_WA.webp</t>
+  </si>
+  <si>
+    <t>San Martino, Italy</t>
+  </si>
+  <si>
+    <t>chainstay</t>
+  </si>
+  <si>
+    <t>bb drop</t>
+  </si>
+  <si>
+    <t>median</t>
+  </si>
+  <si>
+    <t>Wheel diameter</t>
+  </si>
+  <si>
+    <t>Tire width</t>
+  </si>
+  <si>
+    <t>Axle height</t>
   </si>
 </sst>
 </file>
@@ -700,13 +731,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -714,7 +745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -722,7 +753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -730,53 +761,58 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
       <c r="C9">
         <v>420</v>
@@ -788,12 +824,12 @@
         <v>515</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>590</v>
@@ -805,12 +841,12 @@
         <v>625</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -822,12 +858,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
       </c>
       <c r="C12">
         <v>428</v>
@@ -839,12 +875,12 @@
         <v>428</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
       </c>
       <c r="C13">
         <v>69</v>
@@ -856,12 +892,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
       </c>
       <c r="C14">
         <v>73</v>
@@ -872,13 +908,25 @@
       <c r="E14">
         <v>73</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14">
+        <v>428</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
       </c>
       <c r="C15">
         <v>1107.5999999999999</v>
@@ -889,13 +937,32 @@
       <c r="E15">
         <v>1143.7</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1098.885</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1103.269</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1101.788</v>
+      </c>
+      <c r="J15">
+        <f>MEDIAN(G15:I15)</f>
+        <v>1101.788</v>
+      </c>
+      <c r="K15">
+        <v>1107.5999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
       </c>
       <c r="C16">
         <v>428.5</v>
@@ -906,13 +973,33 @@
       <c r="E16">
         <v>459.2</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="1">
+        <v>70.861999999999995</v>
+      </c>
+      <c r="H16" s="1">
+        <v>72.62</v>
+      </c>
+      <c r="I16" s="1">
+        <v>71.099000000000004</v>
+      </c>
+      <c r="J16">
+        <f>MEDIAN(G16:I16)</f>
+        <v>71.099000000000004</v>
+      </c>
+      <c r="K16">
+        <f>J16*K15/J15</f>
+        <v>71.474051632437451</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
       <c r="C17">
         <v>581</v>
@@ -924,12 +1011,12 @@
         <v>612</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
         <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
       </c>
       <c r="C18">
         <v>616.1</v>
@@ -940,13 +1027,22 @@
       <c r="E18">
         <v>630.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
       </c>
       <c r="C19">
         <v>310</v>
@@ -957,13 +1053,24 @@
       <c r="E19">
         <v>310</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19">
+        <f>622 + (G18*25.4)*2</f>
+        <v>736.3</v>
+      </c>
+      <c r="H19">
+        <f>622 + (H18*25.4)*2</f>
+        <v>743.92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
       </c>
       <c r="C20">
         <v>80</v>
@@ -974,13 +1081,24 @@
       <c r="E20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20">
+        <f>G19/2</f>
+        <v>368.15</v>
+      </c>
+      <c r="H20">
+        <f>H19/2</f>
+        <v>371.96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
       </c>
       <c r="C21">
         <v>710</v>
@@ -991,15 +1109,46 @@
       <c r="E21">
         <v>785</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21">
+        <f>C19</f>
+        <v>310</v>
+      </c>
+      <c r="H21">
+        <f>D19</f>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22">
+        <v>58</v>
+      </c>
+      <c r="D22">
+        <v>58</v>
+      </c>
+      <c r="E22">
+        <v>58</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22">
+        <f>G20-G21</f>
+        <v>58.149999999999977</v>
+      </c>
+      <c r="H22">
+        <f>H20-H21</f>
+        <v>61.95999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>43</v>
       </c>
       <c r="C23">
         <v>44</v>
@@ -1011,9 +1160,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24">
         <v>503.7</v>
@@ -1025,29 +1174,29 @@
         <v>503.7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>49</v>
       </c>
       <c r="C29">
         <v>700</v>
@@ -1059,42 +1208,42 @@
         <v>700</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30">
+        <v>2.25</v>
+      </c>
+      <c r="D30">
+        <v>2.25</v>
+      </c>
+      <c r="E30">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>50</v>
       </c>
-      <c r="C30">
-        <v>50</v>
-      </c>
-      <c r="D30">
-        <v>50</v>
-      </c>
-      <c r="E30">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="C31">
+        <v>2.4</v>
+      </c>
+      <c r="D31">
+        <v>2.4</v>
+      </c>
+      <c r="E31">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>51</v>
-      </c>
-      <c r="C31">
-        <v>55</v>
-      </c>
-      <c r="D31">
-        <v>55</v>
-      </c>
-      <c r="E31">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -1102,81 +1251,81 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
         <v>53</v>
-      </c>
-      <c r="B35" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" t="s">
         <v>55</v>
-      </c>
-      <c r="B39" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" t="s">
         <v>57</v>
-      </c>
-      <c r="B40" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="B42">
+        <v>2.4</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B45">
         <v>100</v>
@@ -1184,12 +1333,12 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B47">
         <v>30</v>
@@ -1197,168 +1346,176 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>97</v>
-      </c>
-      <c r="B70" t="s">
-        <v>98</v>
+        <v>95</v>
+      </c>
+      <c r="B70">
+        <v>3299</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>99</v>
-      </c>
-      <c r="B71" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="B71">
+        <v>5899</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>102</v>
-      </c>
-      <c r="B73" t="s">
-        <v>103</v>
+        <v>98</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
